--- a/docs/CRM_Issue_Tracker.xlsx
+++ b/docs/CRM_Issue_Tracker.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Issue Tracker" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issue Tracker'!$A$4:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$4:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,8 +75,49 @@
       <color rgb="001E3A5F"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007A6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="008B0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00003366"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="004B0082"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00005A1F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007A3B00"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -146,8 +189,48 @@
         <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E6DA4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0F0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8FFD4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8C0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -169,11 +252,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="medium">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="medium">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -247,6 +344,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3806,4 +3939,5850 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J146"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ascendons CRM — Test Scenarios &amp; QA Checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total Scenarios: 120  |  Modules: 18  |  Types: Functional · Integration · Security · Edge Case · Regression · Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>TC-ID</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Feature / Scenario</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>Related Issue</t>
+        </is>
+      </c>
+      <c r="J4" s="29" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AUTH &amp; MULTI-TENANCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>User Login - Valid Credentials</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/login with valid email+password
+2. Inspect response</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>200 OK with JWT token; token contains tenantId, userId, roles</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H6" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr"/>
+      <c r="J6" s="31" t="inlineStr"/>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>User Login - Invalid Password</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/login with wrong password</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>401 Unauthorized; no token returned; error message shown</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I7" s="34" t="inlineStr"/>
+      <c r="J7" s="34" t="inlineStr"/>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>JWT Expiry Handling</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>1. Use an expired JWT token in Authorization header
+2. Call any protected endpoint</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>401 Unauthorized; frontend redirects to /login</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr"/>
+      <c r="J8" s="31" t="inlineStr"/>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>TC-004</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Data Isolation</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>1. Log in as Tenant A user
+2. Call GET /leads
+3. Log in as Tenant B user
+4. Call GET /leads</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>Each tenant sees ONLY their own data; no cross-tenant leakage</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H9" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I9" s="34" t="inlineStr">
+        <is>
+          <t>CRM-048</t>
+        </is>
+      </c>
+      <c r="J9" s="34" t="inlineStr">
+        <is>
+          <t>Most critical test</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Role-Based Access - Forbidden Action</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>1. Log in as Field Engineer role
+2. Attempt DELETE /leads/{id}</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>403 Forbidden; action blocked by RBAC</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>CRM-002</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr"/>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>TC-006</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>Password Reset Flow</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>1. POST /auth/forgot-password with email
+2. Check email for reset link
+3. POST /auth/reset-password with token</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>Reset email sent; password updated; old token invalidated</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I11" s="34" t="inlineStr">
+        <is>
+          <t>CRM-006</t>
+        </is>
+      </c>
+      <c r="J11" s="34" t="inlineStr">
+        <is>
+          <t>Email service must be real</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>TC-007</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Tenant Registration</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>1. POST /auth/register with org name, email, password
+2. Verify tenant created in DB</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>201 Created; tenant record; default roles seeded; welcome email sent</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="inlineStr"/>
+      <c r="J12" s="31" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LEAD MANAGEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>TC-008</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>Create Lead - All Required Fields</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /leads/new
+2. Fill all required fields
+3. Submit form</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>Lead created with auto-generated ID (LEAD-YYYY-MM-XXXXX); appears in list</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I14" s="34" t="inlineStr"/>
+      <c r="J14" s="34" t="inlineStr"/>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>TC-009</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Create Lead - Missing Required Field</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>1. Submit lead form without firstName</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Form shows validation error; no API call made; lead not created</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I15" s="31" t="inlineStr">
+        <is>
+          <t>CRM-003</t>
+        </is>
+      </c>
+      <c r="J15" s="31" t="inlineStr"/>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>Lead BANT Score Calculation</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>1. Create a lead with Budget=High, Authority=Decision Maker, Need=Strong, Timeline=Immediate
+2. Check score</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>BANT score ≥ 80; lead classified as Hot</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I16" s="34" t="inlineStr"/>
+      <c r="J16" s="34" t="inlineStr"/>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Lead Status Transition</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>1. Open lead in NEW status
+2. Change status to CONTACTED
+3. Change to QUALIFIED</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>Status updates saved; history log records each transition with timestamp</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H17" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr"/>
+      <c r="J17" s="31" t="inlineStr"/>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>Lead Assignment to User</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>1. Open a lead
+2. Assign to a team member
+3. Team member logs in</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>Assignee sees lead in their queue; notification sent to assignee</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H18" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I18" s="34" t="inlineStr"/>
+      <c r="J18" s="34" t="inlineStr"/>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Lead Conversion to Opportunity</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>1. Open a QUALIFIED lead
+2. Click Convert
+3. Fill opportunity details</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>Opportunity created; lead status set to CONVERTED; linked records visible</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I19" s="31" t="inlineStr"/>
+      <c r="J19" s="31" t="inlineStr"/>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>Bulk Lead Delete</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>1. Select 3 leads via checkbox
+2. Click Bulk Delete
+3. Confirm dialog</t>
+        </is>
+      </c>
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>All 3 leads soft-deleted; removed from list; recoverable from DB</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H20" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I20" s="34" t="inlineStr"/>
+      <c r="J20" s="34" t="inlineStr"/>
+    </row>
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Lead Search &amp; Filter</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>1. Search by company name
+2. Filter by status=NEW
+3. Sort by createdAt DESC</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Only matching leads shown; pagination works correctly</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H21" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I21" s="31" t="inlineStr"/>
+      <c r="J21" s="31" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SALES PIPELINE &amp; OPPORTUNITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>Create Opportunity</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /opportunities/new
+2. Fill deal name, value, stage, close date
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>Opportunity created; visible in pipeline kanban and list view</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H23" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I23" s="34" t="inlineStr"/>
+      <c r="J23" s="34" t="inlineStr"/>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>TC-017</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Move Opportunity Across Pipeline Stages</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>1. Open opportunity
+2. Change stage from Prospecting → Qualification → Proposal</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Stage transitions saved; probability auto-updates per stage; history logged</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H24" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I24" s="31" t="inlineStr"/>
+      <c r="J24" s="31" t="inlineStr"/>
+    </row>
+    <row r="25" ht="70" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>Opportunity Win/Loss</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>1. Set opportunity to Closed Won
+2. Set another to Closed Lost with reason</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>Won: revenue recorded. Lost: reason saved. Both removed from active pipeline.</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H25" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I25" s="34" t="inlineStr"/>
+      <c r="J25" s="34" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ASSETS &amp; EQUIPMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="70" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>TC-019</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Create Asset</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /assets/new
+2. Fill serial no, model, brand, category, account
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>Asset created with auto code (ASSET-YYYY-MM-XXXXX); visible in /assets</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H27" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I27" s="31" t="inlineStr"/>
+      <c r="J27" s="31" t="inlineStr"/>
+    </row>
+    <row r="28" ht="70" customHeight="1">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>Duplicate Serial Number Rejection</t>
+        </is>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>1. Create asset with serialNo=SN001
+2. Try creating another with same serialNo</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>409 Conflict returned; second asset not created; error shown in UI</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H28" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I28" s="34" t="inlineStr"/>
+      <c r="J28" s="34" t="inlineStr"/>
+    </row>
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>TC-021</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Asset Warranty Expiry Alert</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>1. Create asset with warrantyExpiry = today + 25 days
+2. Run AssetWarrantyExpiryScheduler manually</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>Log entry shows 30-day warning for the asset; notification sent (once wired)</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H29" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I29" s="31" t="inlineStr">
+        <is>
+          <t>CRM-012</t>
+        </is>
+      </c>
+      <c r="J29" s="31" t="inlineStr"/>
+    </row>
+    <row r="30" ht="70" customHeight="1">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>TC-022</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>Filter Assets by Account</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /assets?accountId=ACC-001</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>Only assets linked to that account returned; others excluded</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H30" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I30" s="34" t="inlineStr"/>
+      <c r="J30" s="34" t="inlineStr"/>
+    </row>
+    <row r="31" ht="70" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Asset Status Update</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>1. Open asset detail
+2. Change status from ACTIVE to UNDER_REPAIR</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>Status updated; reflected in list view with correct badge color</t>
+        </is>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H31" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I31" s="31" t="inlineStr"/>
+      <c r="J31" s="31" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AMC / CONTRACT MANAGEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="70" customHeight="1">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>Create AMC Contract</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /contracts/new
+2. Select type=AMC, account, assets, SLA config
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>Contract created with number CON-XXXXX; visits auto-generated per visitFrequency</t>
+        </is>
+      </c>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H33" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I33" s="34" t="inlineStr"/>
+      <c r="J33" s="34" t="inlineStr"/>
+    </row>
+    <row r="34" ht="70" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Activate Contract</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>1. Open DRAFT contract
+2. Click Activate</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>Status changes to ACTIVE; start date recorded; SLA clock begins</t>
+        </is>
+      </c>
+      <c r="F34" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H34" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I34" s="31" t="inlineStr"/>
+      <c r="J34" s="31" t="inlineStr"/>
+    </row>
+    <row r="35" ht="70" customHeight="1">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>Contract Visit Auto-WO Creation</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>1. Create contract with visit scheduled for today
+2. Trigger ContractVisitScheduler</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>Work order of type AMC_VISIT auto-created; linked to visit record</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H35" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I35" s="34" t="inlineStr">
+        <is>
+          <t>CRM-048</t>
+        </is>
+      </c>
+      <c r="J35" s="34" t="inlineStr">
+        <is>
+          <t>Check tenant isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="70" customHeight="1">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>Contract Renewal</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>1. Open EXPIRED contract
+2. Click Renew with new dates</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>New contract created; old one marked RENEWED; visits regenerated</t>
+        </is>
+      </c>
+      <c r="F36" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H36" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I36" s="31" t="inlineStr"/>
+      <c r="J36" s="31" t="inlineStr"/>
+    </row>
+    <row r="37" ht="70" customHeight="1">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>TC-028</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>Contract SLA Config Feed to Work Order</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>1. Contract has SLA responseHrs=4, resolutionHrs=8
+2. Create WO from this contract</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>WO.slaDeadline = createdAt + 8h; SLA breach triggers if exceeded</t>
+        </is>
+      </c>
+      <c r="F37" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H37" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I37" s="34" t="inlineStr"/>
+      <c r="J37" s="34" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WORK ORDER MANAGEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="70" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>TC-029</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>Create Work Order</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /work-orders/new
+2. Fill type, priority, asset, account
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>WO created with number WO-XXXXX; status=OPEN; SLA deadline calculated</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H39" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I39" s="31" t="inlineStr"/>
+      <c r="J39" s="31" t="inlineStr"/>
+    </row>
+    <row r="40" ht="70" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>TC-030</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C40" s="34" t="inlineStr">
+        <is>
+          <t>Work Order State Machine - Full Flow</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>1. Create WO (OPEN)
+2. Assign engineer (ASSIGNED)
+3. Engineer marks En Route
+4. Arrive on site (ON_SITE)
+5. Start checklist (IN_PROGRESS)
+6. Complete checklist (COMPLETED)</t>
+        </is>
+      </c>
+      <c r="E40" s="34" t="inlineStr">
+        <is>
+          <t>Each status transition succeeds; invalid transitions (e.g. OPEN→COMPLETED) rejected with 400</t>
+        </is>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H40" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I40" s="34" t="inlineStr"/>
+      <c r="J40" s="34" t="inlineStr"/>
+    </row>
+    <row r="41" ht="70" customHeight="1">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>TC-031</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>SLA Breach Detection</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
+        <is>
+          <t>1. Create WO with slaDeadline = now - 1 hour
+2. Run SlaBreachScheduler</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>WO.slaBreached=true; escalation rule fires if configured</t>
+        </is>
+      </c>
+      <c r="F41" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H41" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I41" s="31" t="inlineStr"/>
+      <c r="J41" s="31" t="inlineStr"/>
+    </row>
+    <row r="42" ht="70" customHeight="1">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>TC-032</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>Assign Engineers to WO</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>1. Open WO in OPEN status
+2. Assign 2 engineers</t>
+        </is>
+      </c>
+      <c r="E42" s="34" t="inlineStr">
+        <is>
+          <t>Status changes to ASSIGNED; both engineers see WO in their queue</t>
+        </is>
+      </c>
+      <c r="F42" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H42" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I42" s="34" t="inlineStr"/>
+      <c r="J42" s="34" t="inlineStr"/>
+    </row>
+    <row r="43" ht="70" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>TC-033</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Reopen Completed Work Order</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>1. WO in COMPLETED status
+2. Click Reopen</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>Status = REOPENED; reopenCount incremented; new SLA deadline set</t>
+        </is>
+      </c>
+      <c r="F43" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H43" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I43" s="31" t="inlineStr"/>
+      <c r="J43" s="31" t="inlineStr"/>
+    </row>
+    <row r="44" ht="70" customHeight="1">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>Parts Deduction on WO Closure</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>1. Add part (qty=2) to WO.partsUsed
+2. Close WO</t>
+        </is>
+      </c>
+      <c r="E44" s="34" t="inlineStr">
+        <is>
+          <t>Product.stockQuantity reduced by 2; StockTransaction created with type=PRODUCTION_OUT</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H44" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I44" s="34" t="inlineStr"/>
+      <c r="J44" s="34" t="inlineStr"/>
+    </row>
+    <row r="45" ht="70" customHeight="1">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Insufficient Stock on WO Closure</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>1. Add part with qty &gt; available stock to WO
+2. Attempt to close WO</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>400 Bad Request: 'Insufficient stock'; WO stays in IN_PROGRESS; stock unchanged</t>
+        </is>
+      </c>
+      <c r="F45" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H45" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I45" s="31" t="inlineStr"/>
+      <c r="J45" s="31" t="inlineStr"/>
+    </row>
+    <row r="46" ht="70" customHeight="1">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>TC-036</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>Checklist Mandatory Item Fail Blocks Completion</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>1. Start checklist with mandatory item
+2. Mark item as FAIL with failureAction=Block
+3. Try to complete checklist</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>Completion blocked; error message shown; WO cannot advance to COMPLETED</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H46" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I46" s="34" t="inlineStr"/>
+      <c r="J46" s="34" t="inlineStr"/>
+    </row>
+    <row r="47" ht="70" customHeight="1">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>TC-037</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>Work Orders</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>Kanban View Displays Correct Columns</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /work-orders
+2. Switch to Kanban view</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>WOs grouped by status; drag is not required but cards show correct status column</t>
+        </is>
+      </c>
+      <c r="F47" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H47" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I47" s="31" t="inlineStr"/>
+      <c r="J47" s="31" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SERVICE REQUESTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="70" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>TC-038</t>
+        </is>
+      </c>
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>Service Requests</t>
+        </is>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>Create Service Request</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /service-requests/new
+2. Fill description, source, priority, account
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>SR created with number SR-XXXXX; status=OPEN; SLA clock starts</t>
+        </is>
+      </c>
+      <c r="F49" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H49" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I49" s="34" t="inlineStr"/>
+      <c r="J49" s="34" t="inlineStr"/>
+    </row>
+    <row r="50" ht="70" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>TC-039</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>Service Requests</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>Acknowledge Service Request</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="inlineStr">
+        <is>
+          <t>1. Open SR in OPEN status
+2. Click Acknowledge</t>
+        </is>
+      </c>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>Status = ACKNOWLEDGED; acknowledgedAt timestamp saved</t>
+        </is>
+      </c>
+      <c r="F50" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H50" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I50" s="31" t="inlineStr"/>
+      <c r="J50" s="31" t="inlineStr"/>
+    </row>
+    <row r="51" ht="70" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>TC-040</t>
+        </is>
+      </c>
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>Service Requests</t>
+        </is>
+      </c>
+      <c r="C51" s="34" t="inlineStr">
+        <is>
+          <t>Convert SR to Work Order</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>1. Open ACKNOWLEDGED SR
+2. Click Convert to WO
+3. Fill WO details</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="inlineStr">
+        <is>
+          <t>WO created and linked to SR; SR status = WO_CREATED; workOrderId populated</t>
+        </is>
+      </c>
+      <c r="F51" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H51" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I51" s="34" t="inlineStr"/>
+      <c r="J51" s="34" t="inlineStr"/>
+    </row>
+    <row r="52" ht="70" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>TC-041</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>Service Requests</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>SR Unacknowledged Escalation</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="inlineStr">
+        <is>
+          <t>1. Create SR with conditionMinutes=30 escalation rule
+2. Wait / manually trigger evaluator after 30 min</t>
+        </is>
+      </c>
+      <c r="E52" s="31" t="inlineStr">
+        <is>
+          <t>EscalationLog created for SR; L1 users notified</t>
+        </is>
+      </c>
+      <c r="F52" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H52" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I52" s="31" t="inlineStr">
+        <is>
+          <t>CRM-046</t>
+        </is>
+      </c>
+      <c r="J52" s="31" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DISPATCH &amp; SCHEDULING</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="70" customHeight="1">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>TC-042</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>View Engineer Schedule for Date</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /dispatch
+2. Select today's date</t>
+        </is>
+      </c>
+      <c r="E54" s="34" t="inlineStr">
+        <is>
+          <t>Engineer schedule tiles appear; availability badges shown (AVAILABLE/ON_JOB/LEAVE)</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H54" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I54" s="34" t="inlineStr"/>
+      <c r="J54" s="34" t="inlineStr"/>
+    </row>
+    <row r="55" ht="70" customHeight="1">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>TC-043</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>Dispatch Work Order to Engineer</t>
+        </is>
+      </c>
+      <c r="D55" s="31" t="inlineStr">
+        <is>
+          <t>1. Open dispatch board
+2. Click Dispatch on open WO
+3. Select AVAILABLE engineer
+4. Confirm</t>
+        </is>
+      </c>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>WO status → ASSIGNED; DispatchAssignment created; EngineerSchedule updated to ON_JOB</t>
+        </is>
+      </c>
+      <c r="F55" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H55" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I55" s="31" t="inlineStr"/>
+      <c r="J55" s="31" t="inlineStr"/>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B56" s="34" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C56" s="34" t="inlineStr">
+        <is>
+          <t>Cannot Dispatch to ON_JOB Engineer</t>
+        </is>
+      </c>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>1. Try to dispatch WO to engineer with availability=ON_JOB</t>
+        </is>
+      </c>
+      <c r="E56" s="34" t="inlineStr">
+        <is>
+          <t>Warning shown; dispatch either blocked or flagged as overload</t>
+        </is>
+      </c>
+      <c r="F56" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H56" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I56" s="34" t="inlineStr"/>
+      <c r="J56" s="34" t="inlineStr"/>
+    </row>
+    <row r="57" ht="70" customHeight="1">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>Reassign Work Order</t>
+        </is>
+      </c>
+      <c r="D57" s="31" t="inlineStr">
+        <is>
+          <t>1. WO assigned to Engineer A
+2. Reassign to Engineer B with reason</t>
+        </is>
+      </c>
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>Old engineer's schedule slot removed; new engineer assigned; audit log entry created</t>
+        </is>
+      </c>
+      <c r="F57" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H57" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I57" s="31" t="inlineStr"/>
+      <c r="J57" s="31" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GEO-TRACKING</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="70" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>Geo-Tracking</t>
+        </is>
+      </c>
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>Engineer Location Update</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>1. POST /geo/location with lat, lng, workOrderId
+2. GET /geo/locations</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>Location saved; TTL set for 24h; latest location returned in GET</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H59" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I59" s="34" t="inlineStr"/>
+      <c r="J59" s="34" t="inlineStr"/>
+    </row>
+    <row r="60" ht="70" customHeight="1">
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t>TC-047</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>Geo-Tracking</t>
+        </is>
+      </c>
+      <c r="C60" s="31" t="inlineStr">
+        <is>
+          <t>Geo-Event: Arrived Triggers WO ON_SITE</t>
+        </is>
+      </c>
+      <c r="D60" s="31" t="inlineStr">
+        <is>
+          <t>1. POST /geo/events with eventType=Arrived, workOrderId of EN_ROUTE WO</t>
+        </is>
+      </c>
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>WO status auto-transitions to ON_SITE; WorkOrderGeoEvent persisted</t>
+        </is>
+      </c>
+      <c r="F60" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H60" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I60" s="31" t="inlineStr"/>
+      <c r="J60" s="31" t="inlineStr"/>
+    </row>
+    <row r="61" ht="70" customHeight="1">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B61" s="34" t="inlineStr">
+        <is>
+          <t>Geo-Tracking</t>
+        </is>
+      </c>
+      <c r="C61" s="34" t="inlineStr">
+        <is>
+          <t>Location TTL Expiry</t>
+        </is>
+      </c>
+      <c r="D61" s="34" t="inlineStr">
+        <is>
+          <t>1. Insert engineer location
+2. Wait 24h (or set TTL to 1s in test)
+3. Query location</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>Record automatically deleted by MongoDB TTL index</t>
+        </is>
+      </c>
+      <c r="F61" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H61" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I61" s="34" t="inlineStr"/>
+      <c r="J61" s="34" t="inlineStr"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SKILL MATRIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="70" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>TC-049</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>Skill Matrix</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>Add Skill to Technician</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /skill-matrix
+2. Enter userId
+3. Add Skill: VRF, EXPERT, with cert details</t>
+        </is>
+      </c>
+      <c r="E63" s="31" t="inlineStr">
+        <is>
+          <t>Skill record created; appears in skills table; proficiency badge shows EXPERT</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H63" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I63" s="31" t="inlineStr"/>
+      <c r="J63" s="31" t="inlineStr"/>
+    </row>
+    <row r="64" ht="70" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
+        <is>
+          <t>TC-050</t>
+        </is>
+      </c>
+      <c r="B64" s="34" t="inlineStr">
+        <is>
+          <t>Skill Matrix</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
+          <t>Add Training Record</t>
+        </is>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>1. Add training: OEM training, score=90, passed=true</t>
+        </is>
+      </c>
+      <c r="E64" s="34" t="inlineStr">
+        <is>
+          <t>Training record saved; pass badge (green tick) shown in table</t>
+        </is>
+      </c>
+      <c r="F64" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H64" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I64" s="34" t="inlineStr"/>
+      <c r="J64" s="34" t="inlineStr"/>
+    </row>
+    <row r="65" ht="70" customHeight="1">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>TC-051</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>Skill Matrix</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>Expiring Certification Alert</t>
+        </is>
+      </c>
+      <c r="D65" s="31" t="inlineStr">
+        <is>
+          <t>1. Add skill with expiryDate = today + 25 days
+2. Call GET /skill-matrix/expiring?days=30</t>
+        </is>
+      </c>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>Skill returned in expiring list; alert should be triggered</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H65" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I65" s="31" t="inlineStr"/>
+      <c r="J65" s="31" t="inlineStr"/>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SPARE PARTS &amp; PARTS REQUESTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="70" customHeight="1">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>TC-052</t>
+        </is>
+      </c>
+      <c r="B67" s="34" t="inlineStr">
+        <is>
+          <t>Parts Requests</t>
+        </is>
+      </c>
+      <c r="C67" s="34" t="inlineStr">
+        <is>
+          <t>Create Parts Request from WO</t>
+        </is>
+      </c>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t>1. Open WO in IN_PROGRESS status
+2. Navigate to /work-orders/{id}/parts
+3. Add parts request</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="inlineStr">
+        <is>
+          <t>PartsRequest created; status=PENDING; WO status may change to PENDING_SPARES</t>
+        </is>
+      </c>
+      <c r="F67" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I67" s="34" t="inlineStr">
+        <is>
+          <t>CRM-045</t>
+        </is>
+      </c>
+      <c r="J67" s="34" t="inlineStr"/>
+    </row>
+    <row r="68" ht="70" customHeight="1">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>TC-053</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>Parts Requests</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>Approve Parts Request</t>
+        </is>
+      </c>
+      <c r="D68" s="31" t="inlineStr">
+        <is>
+          <t>1. Open PENDING parts request in /parts-requests
+2. Click Approve</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>Status = APPROVED; stock reserved; WebSocket push to engineer</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="31" t="inlineStr"/>
+    </row>
+    <row r="69" ht="70" customHeight="1">
+      <c r="A69" s="34" t="inlineStr">
+        <is>
+          <t>TC-054</t>
+        </is>
+      </c>
+      <c r="B69" s="34" t="inlineStr">
+        <is>
+          <t>Parts Requests</t>
+        </is>
+      </c>
+      <c r="C69" s="34" t="inlineStr">
+        <is>
+          <t>Reject Parts Request with Reason</t>
+        </is>
+      </c>
+      <c r="D69" s="34" t="inlineStr">
+        <is>
+          <t>1. Open PENDING parts request
+2. Click Reject
+3. Enter reason</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="inlineStr">
+        <is>
+          <t>Status = REJECTED; reason saved; engineer notified</t>
+        </is>
+      </c>
+      <c r="F69" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I69" s="34" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr"/>
+    </row>
+    <row r="70" ht="70" customHeight="1">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>TC-055</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>Parts Requests</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>Dispatch Parts</t>
+        </is>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>1. APPROVED parts request
+2. Click Dispatch</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>Status = DISPATCHED; dispatchedAt timestamp saved</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="31" t="inlineStr"/>
+    </row>
+    <row r="71" ht="70" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>TC-056</t>
+        </is>
+      </c>
+      <c r="B71" s="34" t="inlineStr">
+        <is>
+          <t>Parts Requests</t>
+        </is>
+      </c>
+      <c r="C71" s="34" t="inlineStr">
+        <is>
+          <t>Receive Parts</t>
+        </is>
+      </c>
+      <c r="D71" s="34" t="inlineStr">
+        <is>
+          <t>1. DISPATCHED parts request
+2. Click Mark Received</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="inlineStr">
+        <is>
+          <t>Status = RECEIVED; receivedAt saved; WO can resume IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="F71" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I71" s="34" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr"/>
+    </row>
+    <row r="72" ht="70" customHeight="1">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>TC-057</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Reorder PO Created on Low Stock</t>
+        </is>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>1. Set product reorderPoint=10, stockQty=12
+2. Close WO consuming 5 units (stockQty → 7)
+3. Check purchase_orders collection</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>Draft PO auto-created for the product; poNumber starts with PO-AUTO-</t>
+        </is>
+      </c>
+      <c r="F72" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>CRM-039</t>
+        </is>
+      </c>
+      <c r="J72" s="31" t="inlineStr">
+        <is>
+          <t>Verify no duplicates</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VENDOR MANAGEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="70" customHeight="1">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>TC-058</t>
+        </is>
+      </c>
+      <c r="B74" s="34" t="inlineStr">
+        <is>
+          <t>Vendors</t>
+        </is>
+      </c>
+      <c r="C74" s="34" t="inlineStr">
+        <is>
+          <t>Create Vendor</t>
+        </is>
+      </c>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /vendors/new
+2. Fill companyName, contactPerson, email, GSTIN
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E74" s="34" t="inlineStr">
+        <is>
+          <t>Vendor created; vendorCode auto-generated (VEN-XXXXX); default rating=3</t>
+        </is>
+      </c>
+      <c r="F74" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I74" s="34" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr"/>
+    </row>
+    <row r="75" ht="70" customHeight="1">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>TC-059</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="inlineStr">
+        <is>
+          <t>Vendors</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>Update Vendor Rating</t>
+        </is>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>1. Open vendor detail
+2. Click 4-star rating
+3. Confirm update</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>POST /vendors/{id}/rating with rating=4; vendor.rating updated; badge reflects change</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="31" t="inlineStr"/>
+    </row>
+    <row r="76" ht="70" customHeight="1">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t>TC-060</t>
+        </is>
+      </c>
+      <c r="B76" s="34" t="inlineStr">
+        <is>
+          <t>Vendors</t>
+        </is>
+      </c>
+      <c r="C76" s="34" t="inlineStr">
+        <is>
+          <t>Blacklist Vendor</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>1. Change vendor status to BLACKLISTED</t>
+        </is>
+      </c>
+      <c r="E76" s="34" t="inlineStr">
+        <is>
+          <t>Vendor marked BLACKLISTED; badge shows red; should be excluded from RFQ auto-suggestions</t>
+        </is>
+      </c>
+      <c r="F76" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I76" s="34" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr"/>
+    </row>
+    <row r="77" ht="70" customHeight="1">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>TC-061</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="inlineStr">
+        <is>
+          <t>Vendors</t>
+        </is>
+      </c>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>Vendor Detail Shows Rate Contracts</t>
+        </is>
+      </c>
+      <c r="D77" s="31" t="inlineStr">
+        <is>
+          <t>1. Create rate contract for vendor
+2. Open vendor detail page</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>Rate contracts section on vendor detail page shows associated contracts</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr">
+        <is>
+          <t>CRM-050</t>
+        </is>
+      </c>
+      <c r="J77" s="31" t="inlineStr"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PROCUREMENT (RFQ / GRN / RATE CONTRACTS / PO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="70" customHeight="1">
+      <c r="A79" s="34" t="inlineStr">
+        <is>
+          <t>TC-062</t>
+        </is>
+      </c>
+      <c r="B79" s="34" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="C79" s="34" t="inlineStr">
+        <is>
+          <t>Create RFQ</t>
+        </is>
+      </c>
+      <c r="D79" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /procurement/rfq
+2. Click Create
+3. Add items, select vendors, set deadline</t>
+        </is>
+      </c>
+      <c r="E79" s="34" t="inlineStr">
+        <is>
+          <t>RFQ created with status=OPEN; RFQ number auto-generated</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I79" s="34" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr"/>
+    </row>
+    <row r="80" ht="70" customHeight="1">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>TC-063</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>Submit Vendor Response</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>1. Open RFQ
+2. POST /procurement/rfq/{id}/vendor-response with vendorId, unitPrice, deliveryDays</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>Vendor response saved under RFQ; visible in comparison table on RFQ detail page</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I80" s="31" t="inlineStr"/>
+      <c r="J80" s="31" t="inlineStr"/>
+    </row>
+    <row r="81" ht="70" customHeight="1">
+      <c r="A81" s="34" t="inlineStr">
+        <is>
+          <t>TC-064</t>
+        </is>
+      </c>
+      <c r="B81" s="34" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="C81" s="34" t="inlineStr">
+        <is>
+          <t>Select Vendor Closes RFQ</t>
+        </is>
+      </c>
+      <c r="D81" s="34" t="inlineStr">
+        <is>
+          <t>1. Open RFQ with at least one vendor response
+2. Click Select Vendor</t>
+        </is>
+      </c>
+      <c r="E81" s="34" t="inlineStr">
+        <is>
+          <t>RFQ status = CLOSED; selectedVendorId populated; other vendors notified (future)</t>
+        </is>
+      </c>
+      <c r="F81" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I81" s="34" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr"/>
+    </row>
+    <row r="82" ht="70" customHeight="1">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="inlineStr">
+        <is>
+          <t>GRN</t>
+        </is>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>Create GRN Against PO</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /procurement/grn
+2. Create GRN: poId, receivedDate, lineItems, qualityStatus</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>GRN created with number GRN-XXXXX; linked to PO; PO status may update to RECEIVING</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="31" t="inlineStr"/>
+    </row>
+    <row r="83" ht="70" customHeight="1">
+      <c r="A83" s="34" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="B83" s="34" t="inlineStr">
+        <is>
+          <t>GRN</t>
+        </is>
+      </c>
+      <c r="C83" s="34" t="inlineStr">
+        <is>
+          <t>GRN Quality Status: Partially Accepted</t>
+        </is>
+      </c>
+      <c r="D83" s="34" t="inlineStr">
+        <is>
+          <t>1. Create GRN with receivedQty &lt; orderedQty for one item
+2. Set qualityStatus=PARTIALLY_ACCEPTED</t>
+        </is>
+      </c>
+      <c r="E83" s="34" t="inlineStr">
+        <is>
+          <t>GRN saved; PO remains in RECEIVING state; remaining qty tracked</t>
+        </is>
+      </c>
+      <c r="F83" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H83" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I83" s="34" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr"/>
+    </row>
+    <row r="84" ht="70" customHeight="1">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>TC-067</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>Rate Contracts</t>
+        </is>
+      </c>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>Create Rate Contract</t>
+        </is>
+      </c>
+      <c r="D84" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /procurement/rate-contracts
+2. Create with vendorId, items, validFrom, validTo</t>
+        </is>
+      </c>
+      <c r="E84" s="31" t="inlineStr">
+        <is>
+          <t>Rate contract created with RC number; status=ACTIVE; appears in active contracts list</t>
+        </is>
+      </c>
+      <c r="F84" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H84" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I84" s="31" t="inlineStr"/>
+      <c r="J84" s="31" t="inlineStr"/>
+    </row>
+    <row r="85" ht="70" customHeight="1">
+      <c r="A85" s="34" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="B85" s="34" t="inlineStr">
+        <is>
+          <t>Rate Contracts</t>
+        </is>
+      </c>
+      <c r="C85" s="34" t="inlineStr">
+        <is>
+          <t>Terminate Rate Contract</t>
+        </is>
+      </c>
+      <c r="D85" s="34" t="inlineStr">
+        <is>
+          <t>1. Open active rate contract
+2. Click Terminate</t>
+        </is>
+      </c>
+      <c r="E85" s="34" t="inlineStr">
+        <is>
+          <t>Status = TERMINATED; no longer appears in active list</t>
+        </is>
+      </c>
+      <c r="F85" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H85" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I85" s="34" t="inlineStr"/>
+      <c r="J85" s="34" t="inlineStr"/>
+    </row>
+    <row r="86" ht="70" customHeight="1">
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>PO Approval</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="inlineStr">
+        <is>
+          <t>Submit PO for Approval - Amount &lt; 50k</t>
+        </is>
+      </c>
+      <c r="D86" s="31" t="inlineStr">
+        <is>
+          <t>1. Create PO with totalAmount=30000
+2. Click Submit for Approval</t>
+        </is>
+      </c>
+      <c r="E86" s="31" t="inlineStr">
+        <is>
+          <t>approvalWorkflow has 1 step (L1 only); status = SUBMITTED</t>
+        </is>
+      </c>
+      <c r="F86" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H86" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I86" s="31" t="inlineStr">
+        <is>
+          <t>CRM-024</t>
+        </is>
+      </c>
+      <c r="J86" s="31" t="inlineStr"/>
+    </row>
+    <row r="87" ht="70" customHeight="1">
+      <c r="A87" s="34" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>PO Approval</t>
+        </is>
+      </c>
+      <c r="C87" s="34" t="inlineStr">
+        <is>
+          <t>Submit PO for Approval - Amount 50k-5L</t>
+        </is>
+      </c>
+      <c r="D87" s="34" t="inlineStr">
+        <is>
+          <t>1. Create PO with totalAmount=200000
+2. Submit for Approval</t>
+        </is>
+      </c>
+      <c r="E87" s="34" t="inlineStr">
+        <is>
+          <t>approvalWorkflow has 2 steps (L1 + L2); status = SUBMITTED</t>
+        </is>
+      </c>
+      <c r="F87" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H87" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I87" s="34" t="inlineStr">
+        <is>
+          <t>CRM-024</t>
+        </is>
+      </c>
+      <c r="J87" s="34" t="inlineStr"/>
+    </row>
+    <row r="88" ht="70" customHeight="1">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>PO Approval</t>
+        </is>
+      </c>
+      <c r="C88" s="31" t="inlineStr">
+        <is>
+          <t>Submit PO for Approval - Amount &gt; 5L</t>
+        </is>
+      </c>
+      <c r="D88" s="31" t="inlineStr">
+        <is>
+          <t>1. Create PO with totalAmount=600000
+2. Submit for Approval</t>
+        </is>
+      </c>
+      <c r="E88" s="31" t="inlineStr">
+        <is>
+          <t>approvalWorkflow has 3 steps (L1 + L2 + L3); status = SUBMITTED</t>
+        </is>
+      </c>
+      <c r="F88" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H88" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I88" s="31" t="inlineStr">
+        <is>
+          <t>CRM-024</t>
+        </is>
+      </c>
+      <c r="J88" s="31" t="inlineStr"/>
+    </row>
+    <row r="89" ht="70" customHeight="1">
+      <c r="A89" s="34" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="B89" s="34" t="inlineStr">
+        <is>
+          <t>PO Approval</t>
+        </is>
+      </c>
+      <c r="C89" s="34" t="inlineStr">
+        <is>
+          <t>L1 Approve → L2 Required Next</t>
+        </is>
+      </c>
+      <c r="D89" s="34" t="inlineStr">
+        <is>
+          <t>1. SUBMITTED PO (L1+L2 workflow)
+2. L1 approver calls POST /approve?level=L1</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="inlineStr">
+        <is>
+          <t>L1 step status = Approved; PO still SUBMITTED; L2 pending</t>
+        </is>
+      </c>
+      <c r="F89" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H89" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I89" s="34" t="inlineStr">
+        <is>
+          <t>CRM-024</t>
+        </is>
+      </c>
+      <c r="J89" s="34" t="inlineStr"/>
+    </row>
+    <row r="90" ht="70" customHeight="1">
+      <c r="A90" s="31" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="B90" s="31" t="inlineStr">
+        <is>
+          <t>PO Approval</t>
+        </is>
+      </c>
+      <c r="C90" s="31" t="inlineStr">
+        <is>
+          <t>Skip L1 and Approve at L2 - Should Fail</t>
+        </is>
+      </c>
+      <c r="D90" s="31" t="inlineStr">
+        <is>
+          <t>1. SUBMITTED PO (L1+L2 workflow)
+2. Try to approve at L2 without L1 approval</t>
+        </is>
+      </c>
+      <c r="E90" s="31" t="inlineStr">
+        <is>
+          <t>400 Bad Request: Level L1 approval required first</t>
+        </is>
+      </c>
+      <c r="F90" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H90" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I90" s="31" t="inlineStr">
+        <is>
+          <t>CRM-024</t>
+        </is>
+      </c>
+      <c r="J90" s="31" t="inlineStr"/>
+    </row>
+    <row r="91" ht="70" customHeight="1">
+      <c r="A91" s="34" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="B91" s="34" t="inlineStr">
+        <is>
+          <t>PO Approval</t>
+        </is>
+      </c>
+      <c r="C91" s="34" t="inlineStr">
+        <is>
+          <t>Reject PO at Any Level</t>
+        </is>
+      </c>
+      <c r="D91" s="34" t="inlineStr">
+        <is>
+          <t>1. SUBMITTED PO
+2. POST /reject?level=L1 with reason</t>
+        </is>
+      </c>
+      <c r="E91" s="34" t="inlineStr">
+        <is>
+          <t>PO status = CANCELLED; rejectionReason saved; step status = Rejected</t>
+        </is>
+      </c>
+      <c r="F91" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H91" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I91" s="34" t="inlineStr">
+        <is>
+          <t>CRM-024</t>
+        </is>
+      </c>
+      <c r="J91" s="34" t="inlineStr"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DEALER MANAGEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="70" customHeight="1">
+      <c r="A93" s="31" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B93" s="31" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>Create Dealer</t>
+        </is>
+      </c>
+      <c r="D93" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /dealers/new
+2. Fill companyName, tier=GOLD, creditLimit=500000
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E93" s="31" t="inlineStr">
+        <is>
+          <t>Dealer created with dealerCode DLR-XXXXX; status=ACTIVE; credit utilization=0%</t>
+        </is>
+      </c>
+      <c r="F93" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H93" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I93" s="31" t="inlineStr"/>
+      <c r="J93" s="31" t="inlineStr"/>
+    </row>
+    <row r="94" ht="70" customHeight="1">
+      <c r="A94" s="34" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B94" s="34" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="C94" s="34" t="inlineStr">
+        <is>
+          <t>Place Dealer Order Within Credit Limit</t>
+        </is>
+      </c>
+      <c r="D94" s="34" t="inlineStr">
+        <is>
+          <t>1. Dealer has creditLimit=100000, currentCreditUsed=0
+2. Place order totalValue=50000</t>
+        </is>
+      </c>
+      <c r="E94" s="34" t="inlineStr">
+        <is>
+          <t>Order created; currentCreditUsed → 50000; credit utilization shows 50%</t>
+        </is>
+      </c>
+      <c r="F94" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I94" s="34" t="inlineStr"/>
+      <c r="J94" s="34" t="inlineStr"/>
+    </row>
+    <row r="95" ht="70" customHeight="1">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B95" s="31" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="C95" s="31" t="inlineStr">
+        <is>
+          <t>Place Order Exceeding Credit Limit</t>
+        </is>
+      </c>
+      <c r="D95" s="31" t="inlineStr">
+        <is>
+          <t>1. Dealer creditLimit=100000, currentCreditUsed=80000
+2. Try placing order totalValue=30000</t>
+        </is>
+      </c>
+      <c r="E95" s="31" t="inlineStr">
+        <is>
+          <t>400 Bad Request: credit limit exceeded; order not created; UI shows error</t>
+        </is>
+      </c>
+      <c r="F95" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H95" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I95" s="31" t="inlineStr"/>
+      <c r="J95" s="31" t="inlineStr"/>
+    </row>
+    <row r="96" ht="70" customHeight="1">
+      <c r="A96" s="34" t="inlineStr">
+        <is>
+          <t>TC-078</t>
+        </is>
+      </c>
+      <c r="B96" s="34" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="C96" s="34" t="inlineStr">
+        <is>
+          <t>Suspend Dealer</t>
+        </is>
+      </c>
+      <c r="D96" s="34" t="inlineStr">
+        <is>
+          <t>1. Open active dealer
+2. Click Suspend</t>
+        </is>
+      </c>
+      <c r="E96" s="34" t="inlineStr">
+        <is>
+          <t>Status = SUSPENDED; badge turns red; suspended dealers cannot place orders</t>
+        </is>
+      </c>
+      <c r="F96" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H96" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I96" s="34" t="inlineStr"/>
+      <c r="J96" s="34" t="inlineStr"/>
+    </row>
+    <row r="97" ht="70" customHeight="1">
+      <c r="A97" s="31" t="inlineStr">
+        <is>
+          <t>TC-079</t>
+        </is>
+      </c>
+      <c r="B97" s="31" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="C97" s="31" t="inlineStr">
+        <is>
+          <t>Dealer Monthly Performance Aggregation</t>
+        </is>
+      </c>
+      <c r="D97" s="31" t="inlineStr">
+        <is>
+          <t>1. Place 3 orders in current month (2 Delivered, 1 Pending)
+2. Trigger performance aggregation or GET /dealers/{id}/performance</t>
+        </is>
+      </c>
+      <c r="E97" s="31" t="inlineStr">
+        <is>
+          <t>actualSales = sum of Delivered order values; openOrders = 1</t>
+        </is>
+      </c>
+      <c r="F97" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H97" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I97" s="31" t="inlineStr">
+        <is>
+          <t>CRM-049</t>
+        </is>
+      </c>
+      <c r="J97" s="31" t="inlineStr">
+        <is>
+          <t>Verify tenant isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="70" customHeight="1">
+      <c r="A98" s="34" t="inlineStr">
+        <is>
+          <t>TC-080</t>
+        </is>
+      </c>
+      <c r="B98" s="34" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="C98" s="34" t="inlineStr">
+        <is>
+          <t>Dealer Tier Badge Display</t>
+        </is>
+      </c>
+      <c r="D98" s="34" t="inlineStr">
+        <is>
+          <t>1. Create dealers with each tier: PLATINUM, GOLD, SILVER, BRONZE
+2. Open /dealers list</t>
+        </is>
+      </c>
+      <c r="E98" s="34" t="inlineStr">
+        <is>
+          <t>Each dealer shows correct colored badge: purple/amber/gray/orange</t>
+        </is>
+      </c>
+      <c r="F98" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H98" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I98" s="34" t="inlineStr"/>
+      <c r="J98" s="34" t="inlineStr"/>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SERVICE ANALYTICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="70" customHeight="1">
+      <c r="A100" s="31" t="inlineStr">
+        <is>
+          <t>TC-081</t>
+        </is>
+      </c>
+      <c r="B100" s="31" t="inlineStr">
+        <is>
+          <t>Service Analytics</t>
+        </is>
+      </c>
+      <c r="C100" s="31" t="inlineStr">
+        <is>
+          <t>KPI Dashboard Loads</t>
+        </is>
+      </c>
+      <c r="D100" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /analytics/service
+2. Wait for all 3 API calls to complete</t>
+        </is>
+      </c>
+      <c r="E100" s="31" t="inlineStr">
+        <is>
+          <t>All 6 KPI cards populated; WO aging buckets show bar chart; no errors</t>
+        </is>
+      </c>
+      <c r="F100" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H100" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I100" s="31" t="inlineStr"/>
+      <c r="J100" s="31" t="inlineStr"/>
+    </row>
+    <row r="101" ht="70" customHeight="1">
+      <c r="A101" s="34" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="B101" s="34" t="inlineStr">
+        <is>
+          <t>Service Analytics</t>
+        </is>
+      </c>
+      <c r="C101" s="34" t="inlineStr">
+        <is>
+          <t>MTTR Calculation</t>
+        </is>
+      </c>
+      <c r="D101" s="34" t="inlineStr">
+        <is>
+          <t>1. Complete 2 WOs: one took 2h, one took 4h
+2. Check /analytics/service/kpis</t>
+        </is>
+      </c>
+      <c r="E101" s="34" t="inlineStr">
+        <is>
+          <t>mttrHours = 3.0 (average of 2h and 4h)</t>
+        </is>
+      </c>
+      <c r="F101" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H101" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I101" s="34" t="inlineStr"/>
+      <c r="J101" s="34" t="inlineStr"/>
+    </row>
+    <row r="102" ht="70" customHeight="1">
+      <c r="A102" s="31" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="B102" s="31" t="inlineStr">
+        <is>
+          <t>Service Analytics</t>
+        </is>
+      </c>
+      <c r="C102" s="31" t="inlineStr">
+        <is>
+          <t>SLA Compliance Rate</t>
+        </is>
+      </c>
+      <c r="D102" s="31" t="inlineStr">
+        <is>
+          <t>1. Complete 4 WOs: 3 within SLA, 1 breached
+2. Check kpis.slaComplianceRatePct</t>
+        </is>
+      </c>
+      <c r="E102" s="31" t="inlineStr">
+        <is>
+          <t>slaComplianceRatePct = 75.0</t>
+        </is>
+      </c>
+      <c r="F102" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H102" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I102" s="31" t="inlineStr"/>
+      <c r="J102" s="31" t="inlineStr"/>
+    </row>
+    <row r="103" ht="70" customHeight="1">
+      <c r="A103" s="34" t="inlineStr">
+        <is>
+          <t>TC-084</t>
+        </is>
+      </c>
+      <c r="B103" s="34" t="inlineStr">
+        <is>
+          <t>Service Analytics</t>
+        </is>
+      </c>
+      <c r="C103" s="34" t="inlineStr">
+        <is>
+          <t>First Time Fix Rate</t>
+        </is>
+      </c>
+      <c r="D103" s="34" t="inlineStr">
+        <is>
+          <t>1. Complete 5 WOs: 4 with reopenCount=0, 1 with reopenCount=1
+2. Check kpis.firstTimeFixRatePct</t>
+        </is>
+      </c>
+      <c r="E103" s="34" t="inlineStr">
+        <is>
+          <t>firstTimeFixRatePct = 80.0</t>
+        </is>
+      </c>
+      <c r="F103" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H103" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I103" s="34" t="inlineStr"/>
+      <c r="J103" s="34" t="inlineStr"/>
+    </row>
+    <row r="104" ht="70" customHeight="1">
+      <c r="A104" s="31" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B104" s="31" t="inlineStr">
+        <is>
+          <t>Service Analytics</t>
+        </is>
+      </c>
+      <c r="C104" s="31" t="inlineStr">
+        <is>
+          <t>Volume by Type/Priority/Status</t>
+        </is>
+      </c>
+      <c r="D104" s="31" t="inlineStr">
+        <is>
+          <t>1. Create WOs with different types and priorities
+2. Call /analytics/service/volume</t>
+        </is>
+      </c>
+      <c r="E104" s="31" t="inlineStr">
+        <is>
+          <t>byType, byPriority, byStatus maps contain correct counts</t>
+        </is>
+      </c>
+      <c r="F104" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H104" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I104" s="31" t="inlineStr"/>
+      <c r="J104" s="31" t="inlineStr"/>
+    </row>
+    <row r="105" ht="70" customHeight="1">
+      <c r="A105" s="34" t="inlineStr">
+        <is>
+          <t>TC-086</t>
+        </is>
+      </c>
+      <c r="B105" s="34" t="inlineStr">
+        <is>
+          <t>Service Analytics</t>
+        </is>
+      </c>
+      <c r="C105" s="34" t="inlineStr">
+        <is>
+          <t>Analytics Cache Invalidation</t>
+        </is>
+      </c>
+      <c r="D105" s="34" t="inlineStr">
+        <is>
+          <t>1. Load /analytics/service/kpis (cached)
+2. Complete a new WO
+3. Reload analytics</t>
+        </is>
+      </c>
+      <c r="E105" s="34" t="inlineStr">
+        <is>
+          <t>Cache TTL of 15 min means stale data is acceptable; document expected behaviour</t>
+        </is>
+      </c>
+      <c r="F105" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H105" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I105" s="34" t="inlineStr"/>
+      <c r="J105" s="34" t="inlineStr"/>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INVENTORY ANALYTICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="70" customHeight="1">
+      <c r="A107" s="31" t="inlineStr">
+        <is>
+          <t>TC-087</t>
+        </is>
+      </c>
+      <c r="B107" s="31" t="inlineStr">
+        <is>
+          <t>Inventory Analytics</t>
+        </is>
+      </c>
+      <c r="C107" s="31" t="inlineStr">
+        <is>
+          <t>Dead Stock Report - 90 Day Bucket</t>
+        </is>
+      </c>
+      <c r="D107" s="31" t="inlineStr">
+        <is>
+          <t>1. Product with last StockTransaction &gt; 90 days ago
+2. GET /analytics/service/inventory/dead-stock</t>
+        </is>
+      </c>
+      <c r="E107" s="31" t="inlineStr">
+        <is>
+          <t>Product appears in deadStock90Days list with correct daysSinceLastMovement</t>
+        </is>
+      </c>
+      <c r="F107" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H107" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I107" s="31" t="inlineStr"/>
+      <c r="J107" s="31" t="inlineStr"/>
+    </row>
+    <row r="108" ht="70" customHeight="1">
+      <c r="A108" s="34" t="inlineStr">
+        <is>
+          <t>TC-088</t>
+        </is>
+      </c>
+      <c r="B108" s="34" t="inlineStr">
+        <is>
+          <t>Inventory Analytics</t>
+        </is>
+      </c>
+      <c r="C108" s="34" t="inlineStr">
+        <is>
+          <t>Reorder Recommendations</t>
+        </is>
+      </c>
+      <c r="D108" s="34" t="inlineStr">
+        <is>
+          <t>1. Product with reorderPoint=20, stockQty=15
+2. GET /analytics/service/inventory/reorder</t>
+        </is>
+      </c>
+      <c r="E108" s="34" t="inlineStr">
+        <is>
+          <t>Product appears in reorder list; suggestedReorderQty = reorderQty or reorderPoint*2</t>
+        </is>
+      </c>
+      <c r="F108" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H108" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I108" s="34" t="inlineStr"/>
+      <c r="J108" s="34" t="inlineStr"/>
+    </row>
+    <row r="109" ht="70" customHeight="1">
+      <c r="A109" s="31" t="inlineStr">
+        <is>
+          <t>TC-089</t>
+        </is>
+      </c>
+      <c r="B109" s="31" t="inlineStr">
+        <is>
+          <t>Inventory Analytics</t>
+        </is>
+      </c>
+      <c r="C109" s="31" t="inlineStr">
+        <is>
+          <t>Top Consumed Parts</t>
+        </is>
+      </c>
+      <c r="D109" s="31" t="inlineStr">
+        <is>
+          <t>1. Multiple PRODUCTION_OUT transactions for different products
+2. GET /analytics/service/inventory/top-consumed?limit=5</t>
+        </is>
+      </c>
+      <c r="E109" s="31" t="inlineStr">
+        <is>
+          <t>Top 5 products by total consumption returned in descending order</t>
+        </is>
+      </c>
+      <c r="F109" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H109" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I109" s="31" t="inlineStr"/>
+      <c r="J109" s="31" t="inlineStr"/>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ESCALATION ENGINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="70" customHeight="1">
+      <c r="A111" s="34" t="inlineStr">
+        <is>
+          <t>TC-090</t>
+        </is>
+      </c>
+      <c r="B111" s="34" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="C111" s="34" t="inlineStr">
+        <is>
+          <t>Create Escalation Rule</t>
+        </is>
+      </c>
+      <c r="D111" s="34" t="inlineStr">
+        <is>
+          <t>1. Navigate to /admin/settings/escalation
+2. Create rule: SLA_BREACH, conditionMinutes=0, level=L1
+3. Save</t>
+        </is>
+      </c>
+      <c r="E111" s="34" t="inlineStr">
+        <is>
+          <t>Rule created; active=true; appears in rules table</t>
+        </is>
+      </c>
+      <c r="F111" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H111" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I111" s="34" t="inlineStr"/>
+      <c r="J111" s="34" t="inlineStr"/>
+    </row>
+    <row r="112" ht="70" customHeight="1">
+      <c r="A112" s="31" t="inlineStr">
+        <is>
+          <t>TC-091</t>
+        </is>
+      </c>
+      <c r="B112" s="31" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="C112" s="31" t="inlineStr">
+        <is>
+          <t>SLA Breach Triggers Escalation</t>
+        </is>
+      </c>
+      <c r="D112" s="31" t="inlineStr">
+        <is>
+          <t>1. Create WO with slaBreached=true
+2. Run escalation evaluator
+3. Check /escalation/logs</t>
+        </is>
+      </c>
+      <c r="E112" s="31" t="inlineStr">
+        <is>
+          <t>EscalationLog created for the WO; no duplicate log if re-run</t>
+        </is>
+      </c>
+      <c r="F112" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H112" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I112" s="31" t="inlineStr"/>
+      <c r="J112" s="31" t="inlineStr"/>
+    </row>
+    <row r="113" ht="70" customHeight="1">
+      <c r="A113" s="34" t="inlineStr">
+        <is>
+          <t>TC-092</t>
+        </is>
+      </c>
+      <c r="B113" s="34" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="C113" s="34" t="inlineStr">
+        <is>
+          <t>No Duplicate Escalation Log</t>
+        </is>
+      </c>
+      <c r="D113" s="34" t="inlineStr">
+        <is>
+          <t>1. WO with slaBreached=true; escalation already fired and unresolved
+2. Run evaluator again</t>
+        </is>
+      </c>
+      <c r="E113" s="34" t="inlineStr">
+        <is>
+          <t>No new EscalationLog created; dedup logic prevents duplicate</t>
+        </is>
+      </c>
+      <c r="F113" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H113" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I113" s="34" t="inlineStr"/>
+      <c r="J113" s="34" t="inlineStr"/>
+    </row>
+    <row r="114" ht="70" customHeight="1">
+      <c r="A114" s="31" t="inlineStr">
+        <is>
+          <t>TC-093</t>
+        </is>
+      </c>
+      <c r="B114" s="31" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="C114" s="31" t="inlineStr">
+        <is>
+          <t>Acknowledge Escalation</t>
+        </is>
+      </c>
+      <c r="D114" s="31" t="inlineStr">
+        <is>
+          <t>1. Open open escalation in /admin/settings/escalation
+2. Click Acknowledge</t>
+        </is>
+      </c>
+      <c r="E114" s="31" t="inlineStr">
+        <is>
+          <t>acknowledgedAt and acknowledgedBy populated; button disabled after</t>
+        </is>
+      </c>
+      <c r="F114" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H114" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I114" s="31" t="inlineStr"/>
+      <c r="J114" s="31" t="inlineStr"/>
+    </row>
+    <row r="115" ht="70" customHeight="1">
+      <c r="A115" s="34" t="inlineStr">
+        <is>
+          <t>TC-094</t>
+        </is>
+      </c>
+      <c r="B115" s="34" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="C115" s="34" t="inlineStr">
+        <is>
+          <t>Resolve Escalation</t>
+        </is>
+      </c>
+      <c r="D115" s="34" t="inlineStr">
+        <is>
+          <t>1. Open acknowledged escalation
+2. Click Resolve</t>
+        </is>
+      </c>
+      <c r="E115" s="34" t="inlineStr">
+        <is>
+          <t>resolvedAt populated; escalation no longer appears in Open Escalations tab</t>
+        </is>
+      </c>
+      <c r="F115" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H115" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I115" s="34" t="inlineStr"/>
+      <c r="J115" s="34" t="inlineStr"/>
+    </row>
+    <row r="116" ht="70" customHeight="1">
+      <c r="A116" s="31" t="inlineStr">
+        <is>
+          <t>TC-095</t>
+        </is>
+      </c>
+      <c r="B116" s="31" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="C116" s="31" t="inlineStr">
+        <is>
+          <t>Inactive Rule Not Evaluated</t>
+        </is>
+      </c>
+      <c r="D116" s="31" t="inlineStr">
+        <is>
+          <t>1. Set escalation rule active=false
+2. Create a WO that would trigger the rule
+3. Run evaluator</t>
+        </is>
+      </c>
+      <c r="E116" s="31" t="inlineStr">
+        <is>
+          <t>No EscalationLog created for inactive rule</t>
+        </is>
+      </c>
+      <c r="F116" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H116" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I116" s="31" t="inlineStr"/>
+      <c r="J116" s="31" t="inlineStr"/>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HR — ATTENDANCE &amp; LEAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="70" customHeight="1">
+      <c r="A118" s="34" t="inlineStr">
+        <is>
+          <t>TC-096</t>
+        </is>
+      </c>
+      <c r="B118" s="34" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C118" s="34" t="inlineStr">
+        <is>
+          <t>Check In with Valid GPS</t>
+        </is>
+      </c>
+      <c r="D118" s="34" t="inlineStr">
+        <is>
+          <t>1. POST /attendance/check-in with valid lat/lng within office geofence</t>
+        </is>
+      </c>
+      <c r="E118" s="34" t="inlineStr">
+        <is>
+          <t>Attendance record created; checkInTime saved; status=PRESENT</t>
+        </is>
+      </c>
+      <c r="F118" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H118" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I118" s="34" t="inlineStr"/>
+      <c r="J118" s="34" t="inlineStr"/>
+    </row>
+    <row r="119" ht="70" customHeight="1">
+      <c r="A119" s="31" t="inlineStr">
+        <is>
+          <t>TC-097</t>
+        </is>
+      </c>
+      <c r="B119" s="31" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C119" s="31" t="inlineStr">
+        <is>
+          <t>Check In Outside Geofence</t>
+        </is>
+      </c>
+      <c r="D119" s="31" t="inlineStr">
+        <is>
+          <t>1. POST /attendance/check-in with lat/lng far from any office location</t>
+        </is>
+      </c>
+      <c r="E119" s="31" t="inlineStr">
+        <is>
+          <t>Check-in flagged as IRREGULAR or rejected; spoofDetected handled</t>
+        </is>
+      </c>
+      <c r="F119" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H119" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I119" s="31" t="inlineStr">
+        <is>
+          <t>CRM-017</t>
+        </is>
+      </c>
+      <c r="J119" s="31" t="inlineStr"/>
+    </row>
+    <row r="120" ht="70" customHeight="1">
+      <c r="A120" s="34" t="inlineStr">
+        <is>
+          <t>TC-098</t>
+        </is>
+      </c>
+      <c r="B120" s="34" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C120" s="34" t="inlineStr">
+        <is>
+          <t>Check Out</t>
+        </is>
+      </c>
+      <c r="D120" s="34" t="inlineStr">
+        <is>
+          <t>1. Check in at 9:00 AM
+2. Check out at 6:00 PM</t>
+        </is>
+      </c>
+      <c r="E120" s="34" t="inlineStr">
+        <is>
+          <t>totalWorkHours = 9.0; status=PRESENT; OT calculated if &gt; shift hours</t>
+        </is>
+      </c>
+      <c r="F120" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H120" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I120" s="34" t="inlineStr"/>
+      <c r="J120" s="34" t="inlineStr"/>
+    </row>
+    <row r="121" ht="70" customHeight="1">
+      <c r="A121" s="31" t="inlineStr">
+        <is>
+          <t>TC-099</t>
+        </is>
+      </c>
+      <c r="B121" s="31" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="C121" s="31" t="inlineStr">
+        <is>
+          <t>Apply for Leave</t>
+        </is>
+      </c>
+      <c r="D121" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /leaves
+2. Apply for 2-day leave with type=CASUAL
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E121" s="31" t="inlineStr">
+        <is>
+          <t>Leave request created with status=PENDING; manager notified</t>
+        </is>
+      </c>
+      <c r="F121" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H121" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I121" s="31" t="inlineStr"/>
+      <c r="J121" s="31" t="inlineStr"/>
+    </row>
+    <row r="122" ht="70" customHeight="1">
+      <c r="A122" s="34" t="inlineStr">
+        <is>
+          <t>TC-100</t>
+        </is>
+      </c>
+      <c r="B122" s="34" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="C122" s="34" t="inlineStr">
+        <is>
+          <t>Approve Leave</t>
+        </is>
+      </c>
+      <c r="D122" s="34" t="inlineStr">
+        <is>
+          <t>1. Manager opens leave request
+2. Approves</t>
+        </is>
+      </c>
+      <c r="E122" s="34" t="inlineStr">
+        <is>
+          <t>Status = APPROVED; leave balance deducted; employee notified</t>
+        </is>
+      </c>
+      <c r="F122" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H122" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I122" s="34" t="inlineStr"/>
+      <c r="J122" s="34" t="inlineStr"/>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RBAC &amp; PERMISSIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="70" customHeight="1">
+      <c r="A124" s="31" t="inlineStr">
+        <is>
+          <t>TC-101</t>
+        </is>
+      </c>
+      <c r="B124" s="31" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C124" s="31" t="inlineStr">
+        <is>
+          <t>Field Engineer Profile Permissions</t>
+        </is>
+      </c>
+      <c r="D124" s="31" t="inlineStr">
+        <is>
+          <t>1. Create user with Field Engineer profile
+2. Attempt to access /admin
+3. Attempt to access /work-orders</t>
+        </is>
+      </c>
+      <c r="E124" s="31" t="inlineStr">
+        <is>
+          <t>/admin returns 403; /work-orders returns 200 with own WOs only</t>
+        </is>
+      </c>
+      <c r="F124" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H124" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I124" s="31" t="inlineStr">
+        <is>
+          <t>CRM-005</t>
+        </is>
+      </c>
+      <c r="J124" s="31" t="inlineStr"/>
+    </row>
+    <row r="125" ht="70" customHeight="1">
+      <c r="A125" s="34" t="inlineStr">
+        <is>
+          <t>TC-102</t>
+        </is>
+      </c>
+      <c r="B125" s="34" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C125" s="34" t="inlineStr">
+        <is>
+          <t>Service Manager Full Field Service Access</t>
+        </is>
+      </c>
+      <c r="D125" s="34" t="inlineStr">
+        <is>
+          <t>1. Create user with Service Manager profile
+2. Access all field service routes</t>
+        </is>
+      </c>
+      <c r="E125" s="34" t="inlineStr">
+        <is>
+          <t>Assets, Contracts, WOs, Dispatch, Skill Matrix, Analytics all accessible</t>
+        </is>
+      </c>
+      <c r="F125" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H125" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I125" s="34" t="inlineStr"/>
+      <c r="J125" s="34" t="inlineStr"/>
+    </row>
+    <row r="126" ht="70" customHeight="1">
+      <c r="A126" s="31" t="inlineStr">
+        <is>
+          <t>TC-103</t>
+        </is>
+      </c>
+      <c r="B126" s="31" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C126" s="31" t="inlineStr">
+        <is>
+          <t>New Tenant Gets Default Profiles</t>
+        </is>
+      </c>
+      <c r="D126" s="31" t="inlineStr">
+        <is>
+          <t>1. Register new tenant
+2. Check profiles collection</t>
+        </is>
+      </c>
+      <c r="E126" s="31" t="inlineStr">
+        <is>
+          <t>8 system profiles cloned for new tenant; all permission objects present including field service modules</t>
+        </is>
+      </c>
+      <c r="F126" s="37" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H126" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I126" s="31" t="inlineStr"/>
+      <c r="J126" s="31" t="inlineStr"/>
+    </row>
+    <row r="127" ht="70" customHeight="1">
+      <c r="A127" s="34" t="inlineStr">
+        <is>
+          <t>TC-104</t>
+        </is>
+      </c>
+      <c r="B127" s="34" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C127" s="34" t="inlineStr">
+        <is>
+          <t>patchMissingPermissions Adds New Modules</t>
+        </is>
+      </c>
+      <c r="D127" s="34" t="inlineStr">
+        <is>
+          <t>1. Existing tenant with old profiles (no DISPATCH permission)
+2. Restart app (runs patchMissingPermissions)
+3. Check profile</t>
+        </is>
+      </c>
+      <c r="E127" s="34" t="inlineStr">
+        <is>
+          <t>DISPATCH, SKILL_MATRIX, VENDORS etc. added to all existing profiles</t>
+        </is>
+      </c>
+      <c r="F127" s="39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H127" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I127" s="34" t="inlineStr"/>
+      <c r="J127" s="34" t="inlineStr"/>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PROPOSALS &amp; INVOICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="70" customHeight="1">
+      <c r="A129" s="31" t="inlineStr">
+        <is>
+          <t>TC-105</t>
+        </is>
+      </c>
+      <c r="B129" s="31" t="inlineStr">
+        <is>
+          <t>Proposals</t>
+        </is>
+      </c>
+      <c r="C129" s="31" t="inlineStr">
+        <is>
+          <t>Create Proposal</t>
+        </is>
+      </c>
+      <c r="D129" s="31" t="inlineStr">
+        <is>
+          <t>1. Navigate to /proposals/new
+2. Fill line items, GST, discount
+3. Submit</t>
+        </is>
+      </c>
+      <c r="E129" s="31" t="inlineStr">
+        <is>
+          <t>Proposal created with version 1; total calculated correctly with GST</t>
+        </is>
+      </c>
+      <c r="F129" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H129" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I129" s="31" t="inlineStr"/>
+      <c r="J129" s="31" t="inlineStr"/>
+    </row>
+    <row r="130" ht="70" customHeight="1">
+      <c r="A130" s="34" t="inlineStr">
+        <is>
+          <t>TC-106</t>
+        </is>
+      </c>
+      <c r="B130" s="34" t="inlineStr">
+        <is>
+          <t>Proposals</t>
+        </is>
+      </c>
+      <c r="C130" s="34" t="inlineStr">
+        <is>
+          <t>Send Proposal to Customer</t>
+        </is>
+      </c>
+      <c r="D130" s="34" t="inlineStr">
+        <is>
+          <t>1. Open DRAFT proposal
+2. Click Send</t>
+        </is>
+      </c>
+      <c r="E130" s="34" t="inlineStr">
+        <is>
+          <t>Status = SENT; sentAt recorded; email notification sent to customer (CRM-007)</t>
+        </is>
+      </c>
+      <c r="F130" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H130" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I130" s="34" t="inlineStr">
+        <is>
+          <t>CRM-007</t>
+        </is>
+      </c>
+      <c r="J130" s="34" t="inlineStr">
+        <is>
+          <t>Email must be wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="70" customHeight="1">
+      <c r="A131" s="31" t="inlineStr">
+        <is>
+          <t>TC-107</t>
+        </is>
+      </c>
+      <c r="B131" s="31" t="inlineStr">
+        <is>
+          <t>Proposals</t>
+        </is>
+      </c>
+      <c r="C131" s="31" t="inlineStr">
+        <is>
+          <t>Accept Proposal</t>
+        </is>
+      </c>
+      <c r="D131" s="31" t="inlineStr">
+        <is>
+          <t>1. Open SENT proposal
+2. Click Accept</t>
+        </is>
+      </c>
+      <c r="E131" s="31" t="inlineStr">
+        <is>
+          <t>Status = ACCEPTED; opportunity stage updated; invoice can be raised</t>
+        </is>
+      </c>
+      <c r="F131" s="32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H131" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I131" s="31" t="inlineStr">
+        <is>
+          <t>CRM-007</t>
+        </is>
+      </c>
+      <c r="J131" s="31" t="inlineStr"/>
+    </row>
+    <row r="132" ht="70" customHeight="1">
+      <c r="A132" s="34" t="inlineStr">
+        <is>
+          <t>TC-108</t>
+        </is>
+      </c>
+      <c r="B132" s="34" t="inlineStr">
+        <is>
+          <t>Proposals</t>
+        </is>
+      </c>
+      <c r="C132" s="34" t="inlineStr">
+        <is>
+          <t>Proposal Versioning</t>
+        </is>
+      </c>
+      <c r="D132" s="34" t="inlineStr">
+        <is>
+          <t>1. Revise an existing proposal</t>
+        </is>
+      </c>
+      <c r="E132" s="34" t="inlineStr">
+        <is>
+          <t>New version created (v2); old version archived; only latest shown by default</t>
+        </is>
+      </c>
+      <c r="F132" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H132" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I132" s="34" t="inlineStr"/>
+      <c r="J132" s="34" t="inlineStr"/>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SECURITY &amp; INFRASTRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="70" customHeight="1">
+      <c r="A134" s="31" t="inlineStr">
+        <is>
+          <t>TC-109</t>
+        </is>
+      </c>
+      <c r="B134" s="31" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C134" s="31" t="inlineStr">
+        <is>
+          <t>Credentials Not in Source Code</t>
+        </is>
+      </c>
+      <c r="D134" s="31" t="inlineStr">
+        <is>
+          <t>1. Review application.properties in repo
+2. Verify no plaintext credentials</t>
+        </is>
+      </c>
+      <c r="E134" s="31" t="inlineStr">
+        <is>
+          <t>All secrets reference environment variables; no hardcoded passwords or URIs</t>
+        </is>
+      </c>
+      <c r="F134" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H134" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I134" s="31" t="inlineStr">
+        <is>
+          <t>CRM-001</t>
+        </is>
+      </c>
+      <c r="J134" s="31" t="inlineStr">
+        <is>
+          <t>P0 - fix immediately</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="70" customHeight="1">
+      <c r="A135" s="34" t="inlineStr">
+        <is>
+          <t>TC-110</t>
+        </is>
+      </c>
+      <c r="B135" s="34" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C135" s="34" t="inlineStr">
+        <is>
+          <t>SQL/NoSQL Injection Prevention</t>
+        </is>
+      </c>
+      <c r="D135" s="34" t="inlineStr">
+        <is>
+          <t>1. POST /leads with firstName = '{$where: function(){return true}}'
+2. Inspect DB query</t>
+        </is>
+      </c>
+      <c r="E135" s="34" t="inlineStr">
+        <is>
+          <t>Spring Data MongoDB parameterises queries; injection attempt harmless</t>
+        </is>
+      </c>
+      <c r="F135" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H135" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I135" s="34" t="inlineStr"/>
+      <c r="J135" s="34" t="inlineStr"/>
+    </row>
+    <row r="136" ht="70" customHeight="1">
+      <c r="A136" s="31" t="inlineStr">
+        <is>
+          <t>TC-111</t>
+        </is>
+      </c>
+      <c r="B136" s="31" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C136" s="31" t="inlineStr">
+        <is>
+          <t>XSS Prevention in Frontend</t>
+        </is>
+      </c>
+      <c r="D136" s="31" t="inlineStr">
+        <is>
+          <t>1. Create lead with name = '&lt;script&gt;alert(1)&lt;/script&gt;'
+2. View lead detail page</t>
+        </is>
+      </c>
+      <c r="E136" s="31" t="inlineStr">
+        <is>
+          <t>Script not executed; React escapes output; name shown as literal text</t>
+        </is>
+      </c>
+      <c r="F136" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H136" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I136" s="31" t="inlineStr"/>
+      <c r="J136" s="31" t="inlineStr"/>
+    </row>
+    <row r="137" ht="70" customHeight="1">
+      <c r="A137" s="34" t="inlineStr">
+        <is>
+          <t>TC-112</t>
+        </is>
+      </c>
+      <c r="B137" s="34" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C137" s="34" t="inlineStr">
+        <is>
+          <t>CORS Policy Enforcement</t>
+        </is>
+      </c>
+      <c r="D137" s="34" t="inlineStr">
+        <is>
+          <t>1. Send request from disallowed origin (http://evil.com)
+2. Check response headers</t>
+        </is>
+      </c>
+      <c r="E137" s="34" t="inlineStr">
+        <is>
+          <t>Request blocked or Access-Control-Allow-Origin header absent/mismatched</t>
+        </is>
+      </c>
+      <c r="F137" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H137" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I137" s="34" t="inlineStr">
+        <is>
+          <t>CRM-037</t>
+        </is>
+      </c>
+      <c r="J137" s="34" t="inlineStr"/>
+    </row>
+    <row r="138" ht="70" customHeight="1">
+      <c r="A138" s="31" t="inlineStr">
+        <is>
+          <t>TC-113</t>
+        </is>
+      </c>
+      <c r="B138" s="31" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C138" s="31" t="inlineStr">
+        <is>
+          <t>Rate Limiting / Brute Force Protection</t>
+        </is>
+      </c>
+      <c r="D138" s="31" t="inlineStr">
+        <is>
+          <t>1. Send 20 failed login attempts from same IP within 1 minute</t>
+        </is>
+      </c>
+      <c r="E138" s="31" t="inlineStr">
+        <is>
+          <t>After threshold, subsequent attempts return 429 Too Many Requests (if implemented)</t>
+        </is>
+      </c>
+      <c r="F138" s="36" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H138" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I138" s="31" t="inlineStr"/>
+      <c r="J138" s="31" t="inlineStr">
+        <is>
+          <t>Not yet implemented - log as feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE &amp; EDGE CASES</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="70" customHeight="1">
+      <c r="A140" s="34" t="inlineStr">
+        <is>
+          <t>TC-114</t>
+        </is>
+      </c>
+      <c r="B140" s="34" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C140" s="34" t="inlineStr">
+        <is>
+          <t>Large Dataset Pagination</t>
+        </is>
+      </c>
+      <c r="D140" s="34" t="inlineStr">
+        <is>
+          <t>1. Seed 1000 leads
+2. GET /leads?page=0&amp;size=20</t>
+        </is>
+      </c>
+      <c r="E140" s="34" t="inlineStr">
+        <is>
+          <t>Response in &lt; 500ms; exactly 20 records; totalElements=1000</t>
+        </is>
+      </c>
+      <c r="F140" s="40" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H140" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I140" s="34" t="inlineStr"/>
+      <c r="J140" s="34" t="inlineStr"/>
+    </row>
+    <row r="141" ht="70" customHeight="1">
+      <c r="A141" s="31" t="inlineStr">
+        <is>
+          <t>TC-115</t>
+        </is>
+      </c>
+      <c r="B141" s="31" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C141" s="31" t="inlineStr">
+        <is>
+          <t>EscalationService findAll() Under Load</t>
+        </is>
+      </c>
+      <c r="D141" s="31" t="inlineStr">
+        <is>
+          <t>1. Seed 10 tenants × 50 escalation rules each
+2. Trigger evaluateAllRules()</t>
+        </is>
+      </c>
+      <c r="E141" s="31" t="inlineStr">
+        <is>
+          <t>All 500 rules evaluated without memory spike; completes in &lt; 30s</t>
+        </is>
+      </c>
+      <c r="F141" s="40" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H141" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I141" s="31" t="inlineStr">
+        <is>
+          <t>CRM-046</t>
+        </is>
+      </c>
+      <c r="J141" s="31" t="inlineStr"/>
+    </row>
+    <row r="142" ht="70" customHeight="1">
+      <c r="A142" s="34" t="inlineStr">
+        <is>
+          <t>TC-116</t>
+        </is>
+      </c>
+      <c r="B142" s="34" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C142" s="34" t="inlineStr">
+        <is>
+          <t>DealerPerformanceService Aggregation at Scale</t>
+        </is>
+      </c>
+      <c r="D142" s="34" t="inlineStr">
+        <is>
+          <t>1. Seed 5 tenants × 500 orders each
+2. Trigger monthly aggregation</t>
+        </is>
+      </c>
+      <c r="E142" s="34" t="inlineStr">
+        <is>
+          <t>Aggregation completes without OOM; per-tenant data correct</t>
+        </is>
+      </c>
+      <c r="F142" s="40" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H142" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I142" s="34" t="inlineStr">
+        <is>
+          <t>CRM-049</t>
+        </is>
+      </c>
+      <c r="J142" s="34" t="inlineStr"/>
+    </row>
+    <row r="143" ht="70" customHeight="1">
+      <c r="A143" s="31" t="inlineStr">
+        <is>
+          <t>TC-117</t>
+        </is>
+      </c>
+      <c r="B143" s="31" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="C143" s="31" t="inlineStr">
+        <is>
+          <t>Soft Delete Excludes Records from All Queries</t>
+        </is>
+      </c>
+      <c r="D143" s="31" t="inlineStr">
+        <is>
+          <t>1. Create and then delete a lead
+2. GET /leads; GET /leads/{id}</t>
+        </is>
+      </c>
+      <c r="E143" s="31" t="inlineStr">
+        <is>
+          <t>Deleted lead absent from list; GET by ID returns 404</t>
+        </is>
+      </c>
+      <c r="F143" s="39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H143" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I143" s="31" t="inlineStr"/>
+      <c r="J143" s="31" t="inlineStr"/>
+    </row>
+    <row r="144" ht="70" customHeight="1">
+      <c r="A144" s="34" t="inlineStr">
+        <is>
+          <t>TC-118</t>
+        </is>
+      </c>
+      <c r="B144" s="34" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="C144" s="34" t="inlineStr">
+        <is>
+          <t>Concurrent WO Closure - Stock Race Condition</t>
+        </is>
+      </c>
+      <c r="D144" s="34" t="inlineStr">
+        <is>
+          <t>1. Set stock qty=5 for a part
+2. Simultaneously close 2 WOs each consuming 5 units</t>
+        </is>
+      </c>
+      <c r="E144" s="34" t="inlineStr">
+        <is>
+          <t>Only one closure succeeds; the other gets 400 Insufficient Stock; final stock ≥ 0</t>
+        </is>
+      </c>
+      <c r="F144" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H144" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I144" s="34" t="inlineStr"/>
+      <c r="J144" s="34" t="inlineStr">
+        <is>
+          <t>Verify with load test</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="70" customHeight="1">
+      <c r="A145" s="31" t="inlineStr">
+        <is>
+          <t>TC-119</t>
+        </is>
+      </c>
+      <c r="B145" s="31" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="C145" s="31" t="inlineStr">
+        <is>
+          <t>PO Auto-Reorder Deduplication</t>
+        </is>
+      </c>
+      <c r="D145" s="31" t="inlineStr">
+        <is>
+          <t>1. Close WO that triggers reorder for Product X
+2. Immediately close another WO using Product X</t>
+        </is>
+      </c>
+      <c r="E145" s="31" t="inlineStr">
+        <is>
+          <t>Only one draft reorder PO created for Product X; second run detects existing draft and skips</t>
+        </is>
+      </c>
+      <c r="F145" s="38" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H145" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I145" s="31" t="inlineStr">
+        <is>
+          <t>CRM-039</t>
+        </is>
+      </c>
+      <c r="J145" s="31" t="inlineStr"/>
+    </row>
+    <row r="146" ht="70" customHeight="1">
+      <c r="A146" s="34" t="inlineStr">
+        <is>
+          <t>TC-120</t>
+        </is>
+      </c>
+      <c r="B146" s="34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="C146" s="34" t="inlineStr">
+        <is>
+          <t>Sidebar Navigation Permissions</t>
+        </is>
+      </c>
+      <c r="D146" s="34" t="inlineStr">
+        <is>
+          <t>1. Log in as Field Engineer
+2. Inspect sidebar</t>
+        </is>
+      </c>
+      <c r="E146" s="34" t="inlineStr">
+        <is>
+          <t>Only FIELD_SERVICE and HR sections visible; CRM/Admin/Procurement hidden</t>
+        </is>
+      </c>
+      <c r="F146" s="39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H146" s="33" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="I146" s="34" t="inlineStr">
+        <is>
+          <t>CRM-043</t>
+        </is>
+      </c>
+      <c r="J146" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:J4"/>
+  <mergeCells count="24">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A92:J92"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A110:J110"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A128:J128"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A99:J99"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A139:J139"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>